--- a/circularis_rel/docs/plantillas/carga_inicial.xlsx
+++ b/circularis_rel/docs/plantillas/carga_inicial.xlsx
@@ -1525,7 +1525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1540,18 +1540,19 @@
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="32" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
-    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="32" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="21" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1617,60 +1618,65 @@
       </c>
       <c r="M1" s="5" t="inlineStr">
         <is>
+          <t>usa_horometro</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
           <t>numero_serie</t>
         </is>
       </c>
-      <c r="N1" s="5" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>fabricante</t>
         </is>
       </c>
-      <c r="O1" s="5" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>modelo</t>
         </is>
       </c>
-      <c r="P1" s="5" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>proveedor</t>
         </is>
       </c>
-      <c r="Q1" s="5" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>fecha_instalacion</t>
         </is>
       </c>
-      <c r="R1" s="5" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>ancho_mm</t>
         </is>
       </c>
-      <c r="S1" s="5" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>alto_mm</t>
         </is>
       </c>
-      <c r="T1" s="5" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>largo_mm</t>
         </is>
       </c>
-      <c r="U1" s="5" t="inlineStr">
+      <c r="V1" s="5" t="inlineStr">
         <is>
           <t>peso_kg</t>
         </is>
       </c>
-      <c r="V1" s="5" t="inlineStr">
+      <c r="W1" s="5" t="inlineStr">
         <is>
           <t>condiciones_almacenamiento</t>
         </is>
       </c>
-      <c r="W1" s="5" t="inlineStr">
+      <c r="X1" s="5" t="inlineStr">
         <is>
           <t>caracteristicas_tecnicas</t>
         </is>
       </c>
-      <c r="X1" s="5" t="inlineStr">
+      <c r="Y1" s="5" t="inlineStr">
         <is>
           <t>ruta_documentos</t>
         </is>
@@ -1737,22 +1743,27 @@
           <t>Tiempo de ciclo teórico en segundos (para RO/OEE)</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr"/>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>SI si tiene horómetro: el parte pide la lectura (horas medidas). opciones: SI, NO</t>
+        </is>
+      </c>
       <c r="N2" s="4" t="inlineStr"/>
       <c r="O2" s="4" t="inlineStr"/>
       <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>DD/MM/AAAA</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr"/>
       <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
       <c r="V2" s="4" t="inlineStr"/>
       <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr"/>
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>Carpeta con planos, manuales y catálogos</t>
         </is>
@@ -1760,12 +1771,15 @@
     </row>
     <row r="3"/>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="D3:D503" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elegí un valor de la lista" type="list">
       <formula1>"PREPROCESADO,LAVADO,SECADO,FORMULACION,EXTRUSION,ACONDICIONAMIENTO"</formula1>
     </dataValidation>
     <dataValidation sqref="I3:I503" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elegí un valor de la lista" type="list">
       <formula1>"KG,FARDOS,DURMIENTES,NINGUNA"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M3:M503" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elegí un valor de la lista" type="list">
+      <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
